--- a/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27010"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="657" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E8E2733-5C21-4F90-8710-45C8A7DBC4A3}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{369A08B9-F5C2-4DB4-A5CB-8B028286B057}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -445,12 +445,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -572,50 +572,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -638,7 +598,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -831,52 +791,13 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
@@ -886,25 +807,6 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="43" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -913,17 +815,83 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1229,36 +1197,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57C0583-E09D-4D51-BD15-84D2EB417CAA}">
-  <dimension ref="A1:S81"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="4" customWidth="1"/>
-    <col min="2" max="3" width="41.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="23.85546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="35" style="4" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="65.140625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" style="4" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="4"/>
-    <col min="13" max="13" width="8.85546875" style="4"/>
-    <col min="14" max="14" width="25.85546875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="23.28515625" style="4" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="4"/>
+    <col min="1" max="1" width="15.7109375" style="115" customWidth="1"/>
+    <col min="2" max="3" width="41.7109375" style="115" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="118" customWidth="1"/>
+    <col min="5" max="5" width="28.5703125" style="115" customWidth="1"/>
+    <col min="6" max="6" width="35" style="115" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="116" customWidth="1"/>
+    <col min="8" max="8" width="20.140625" style="115" customWidth="1"/>
+    <col min="9" max="9" width="65.140625" style="115" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" style="115" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="115"/>
+    <col min="13" max="13" width="8.85546875" style="115"/>
+    <col min="14" max="14" width="25.85546875" style="115" customWidth="1"/>
+    <col min="15" max="15" width="23.28515625" style="115" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:18" s="4" customFormat="1">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="98" t="s">
+      <c r="D1" s="85" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -1282,10 +1250,10 @@
       <c r="K1" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="109" t="s">
+      <c r="L1" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="107" t="s">
+      <c r="M1" s="87" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="64" t="s">
@@ -1304,17 +1272,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="9" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A2" s="54">
+    <row r="2" spans="1:18" s="9" customFormat="1" ht="54.75" customHeight="1">
+      <c r="A2" s="92">
         <v>130247</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="105" t="s">
+      <c r="C2" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="106">
+      <c r="D2" s="86">
         <v>1100000</v>
       </c>
       <c r="E2" s="45" t="s">
@@ -1332,7 +1300,7 @@
       <c r="I2" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="111" t="s">
+      <c r="J2" s="91" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="69"/>
@@ -1349,14 +1317,13 @@
       <c r="P2" s="68"/>
       <c r="Q2" s="68"/>
       <c r="R2" s="68"/>
-      <c r="S2" s="25"/>
-    </row>
-    <row r="3" spans="1:19" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A3" s="76"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="96" t="s">
+    </row>
+    <row r="3" spans="1:18" s="10" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A3" s="93"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="83" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="14" t="s">
@@ -1372,7 +1339,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="20"/>
-      <c r="K3" s="110"/>
+      <c r="K3" s="90"/>
       <c r="L3" s="20"/>
       <c r="M3" s="20"/>
       <c r="N3" s="25" t="s">
@@ -1384,14 +1351,13 @@
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
-      <c r="S3" s="20"/>
-    </row>
-    <row r="4" spans="1:19" s="10" customFormat="1" ht="45.75">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="103"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="96"/>
+    </row>
+    <row r="4" spans="1:18" s="10" customFormat="1" ht="45.75">
+      <c r="A4" s="94"/>
+      <c r="B4" s="96"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="112" t="s">
         <v>30</v>
       </c>
@@ -1401,7 +1367,7 @@
       <c r="H4" s="113"/>
       <c r="I4" s="114"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="108"/>
+      <c r="K4" s="88"/>
       <c r="L4" s="20"/>
       <c r="M4" s="20"/>
       <c r="N4" s="25" t="s">
@@ -1413,9 +1379,8 @@
       <c r="P4" s="25"/>
       <c r="Q4" s="25"/>
       <c r="R4" s="25"/>
-      <c r="S4" s="20"/>
-    </row>
-    <row r="5" spans="1:19" s="10" customFormat="1" ht="45.75">
+    </row>
+    <row r="5" spans="1:18" s="10" customFormat="1" ht="45.75">
       <c r="A5" s="74">
         <v>94293</v>
       </c>
@@ -1460,9 +1425,8 @@
       <c r="P5" s="25"/>
       <c r="Q5" s="25"/>
       <c r="R5" s="25"/>
-      <c r="S5" s="20"/>
-    </row>
-    <row r="6" spans="1:19" s="10" customFormat="1" ht="65.25" customHeight="1">
+    </row>
+    <row r="6" spans="1:18" s="10" customFormat="1" ht="65.25" customHeight="1">
       <c r="A6" s="11">
         <v>130474</v>
       </c>
@@ -1493,7 +1457,7 @@
       <c r="J6" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="108"/>
+      <c r="K6" s="88"/>
       <c r="L6" s="20" t="s">
         <v>24</v>
       </c>
@@ -1507,9 +1471,8 @@
       <c r="P6" s="25"/>
       <c r="Q6" s="25"/>
       <c r="R6" s="25"/>
-      <c r="S6" s="20"/>
-    </row>
-    <row r="7" spans="1:19" s="10" customFormat="1">
+    </row>
+    <row r="7" spans="1:18" s="10" customFormat="1">
       <c r="A7" s="42"/>
       <c r="B7" s="42"/>
       <c r="C7" s="43"/>
@@ -1520,803 +1483,10 @@
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
-    <row r="8" spans="1:19" s="10" customFormat="1">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="45"/>
-    </row>
-    <row r="9" spans="1:19" s="10" customFormat="1">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="45"/>
-    </row>
-    <row r="10" spans="1:19" s="9" customFormat="1">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="45"/>
-    </row>
-    <row r="11" spans="1:19" s="9" customFormat="1">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="45"/>
-    </row>
-    <row r="12" spans="1:19" s="9" customFormat="1">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="45"/>
-    </row>
-    <row r="13" spans="1:19" s="9" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="45"/>
-    </row>
-    <row r="14" spans="1:19" s="9" customFormat="1">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="45"/>
-    </row>
-    <row r="15" spans="1:19" s="9" customFormat="1">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="45"/>
-    </row>
-    <row r="16" spans="1:19" s="9" customFormat="1">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="45"/>
-    </row>
-    <row r="17" spans="1:9" s="9" customFormat="1">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="45"/>
-    </row>
-    <row r="18" spans="1:9" s="9" customFormat="1" ht="93.75" customHeight="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="48"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="83"/>
-      <c r="F19" s="51"/>
-      <c r="H19" s="51"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="80"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
-      <c r="F20" s="51"/>
-      <c r="H20" s="51"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="80"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="83"/>
-      <c r="G21" s="50"/>
-      <c r="I21" s="52"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="80"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="83"/>
-      <c r="H22"/>
-      <c r="I22" s="52"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="83"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="80"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="56"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="57"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="59"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="27"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="27"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="27"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="27"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="27"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="27"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="27"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="29"/>
-      <c r="H62" s="27"/>
-      <c r="I62" s="27"/>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="27"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="27"/>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="27"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="27"/>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="27"/>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="27"/>
-      <c r="B68" s="27"/>
-      <c r="C68" s="27"/>
-      <c r="D68" s="34"/>
-      <c r="E68" s="27"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="27"/>
-      <c r="I68" s="27"/>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="27"/>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="27"/>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="27"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="27"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="27"/>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="27"/>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="27"/>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-    </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="27"/>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="27"/>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="27"/>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="27"/>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="27"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="29"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="27"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="27"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="29"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-    </row>
-    <row r="81" spans="1:9">
-      <c r="A81" s="27"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
+    <row r="8" spans="1:18">
+      <c r="C8" s="117"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="C19:C25"/>
-    <mergeCell ref="D19:D25"/>
-  </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{B9B142FD-CB0E-4605-A61A-C94195D80DBA}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable EnergyEnergy Infrastructure,   Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid"</formula1>
@@ -2347,7 +1517,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E3:E31</xm:sqref>
+          <xm:sqref>E3:E12</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2375,16 +1545,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97" t="s">
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="98" t="s">
+      <c r="D1" s="85" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="6" t="s">
@@ -2481,11 +1651,7 @@
       <c r="S2" s="70"/>
     </row>
     <row r="3" spans="1:19" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="96" t="s">
+      <c r="E3" s="83" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="14" t="s">
@@ -2513,11 +1679,10 @@
       <c r="S3" s="9"/>
     </row>
     <row r="4" spans="1:19" s="10" customFormat="1" ht="45.75">
-      <c r="A4" s="92"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="95"/>
-      <c r="E4" s="96"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="83"/>
       <c r="F4" s="14" t="s">
         <v>30</v>
       </c>
@@ -2764,58 +1929,58 @@
       <c r="H18" s="48"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="83"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="103"/>
       <c r="F19" s="51"/>
       <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="80"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="103"/>
       <c r="F20" s="51"/>
       <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="80"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="83"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="103"/>
       <c r="G21" s="50"/>
       <c r="I21" s="52"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="80"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="82"/>
-      <c r="D22" s="83"/>
+      <c r="A22" s="100"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="103"/>
       <c r="H22"/>
       <c r="I22" s="52"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="103"/>
       <c r="F23" s="53"/>
       <c r="G23" s="50"/>
       <c r="H23" s="52"/>
       <c r="I23" s="52"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
-      <c r="D24" s="83"/>
+      <c r="A24" s="100"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="103"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="80"/>
-      <c r="B25" s="81"/>
-      <c r="C25" s="82"/>
-      <c r="D25" s="83"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="103"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="56"/>
@@ -3803,10 +2968,10 @@
       <c r="I20" s="25"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="85"/>
-      <c r="B21" s="84"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="87"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="104"/>
+      <c r="C21" s="106"/>
+      <c r="D21" s="107"/>
       <c r="E21" s="27"/>
       <c r="F21" s="28"/>
       <c r="G21" s="29"/>
@@ -3814,10 +2979,10 @@
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="85"/>
-      <c r="B22" s="84"/>
-      <c r="C22" s="86"/>
-      <c r="D22" s="87"/>
+      <c r="A22" s="105"/>
+      <c r="B22" s="104"/>
+      <c r="C22" s="106"/>
+      <c r="D22" s="107"/>
       <c r="E22" s="27"/>
       <c r="F22" s="28"/>
       <c r="G22" s="29"/>
@@ -3825,10 +2990,10 @@
       <c r="I22" s="27"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="85"/>
-      <c r="B23" s="84"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="87"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="106"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="27"/>
       <c r="F23" s="27"/>
       <c r="G23" s="26"/>
@@ -3836,10 +3001,10 @@
       <c r="I23" s="30"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="85"/>
-      <c r="B24" s="84"/>
-      <c r="C24" s="86"/>
-      <c r="D24" s="87"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="104"/>
+      <c r="C24" s="106"/>
+      <c r="D24" s="107"/>
       <c r="E24" s="27"/>
       <c r="F24" s="27"/>
       <c r="G24" s="29"/>
@@ -3847,10 +3012,10 @@
       <c r="I24" s="30"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="85"/>
-      <c r="B25" s="84"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="87"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="104"/>
+      <c r="C25" s="106"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="27"/>
       <c r="F25" s="32"/>
       <c r="G25" s="26"/>
@@ -3858,10 +3023,10 @@
       <c r="I25" s="30"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="85"/>
-      <c r="B26" s="84"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="87"/>
+      <c r="A26" s="105"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="107"/>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="29"/>
@@ -3869,10 +3034,10 @@
       <c r="I26" s="27"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="85"/>
-      <c r="B27" s="84"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="87"/>
+      <c r="A27" s="105"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="106"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="27"/>
       <c r="F27" s="27"/>
       <c r="G27" s="29"/>
@@ -4545,7 +3710,7 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="108" t="s">
         <v>52</v>
       </c>
       <c r="B2" t="s">
@@ -4556,7 +3721,7 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="88"/>
+      <c r="A3" s="108"/>
       <c r="B3" t="s">
         <v>55</v>
       </c>
@@ -4565,7 +3730,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="88"/>
+      <c r="A4" s="108"/>
       <c r="B4" t="s">
         <v>57</v>
       </c>
@@ -4574,7 +3739,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="109" t="s">
         <v>59</v>
       </c>
       <c r="B5" t="s">
@@ -4585,7 +3750,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="89"/>
+      <c r="A6" s="109"/>
       <c r="B6" t="s">
         <v>61</v>
       </c>
@@ -4594,7 +3759,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="89"/>
+      <c r="A7" s="109"/>
       <c r="B7" t="s">
         <v>33</v>
       </c>
@@ -4603,7 +3768,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="89"/>
+      <c r="A8" s="109"/>
       <c r="B8" t="s">
         <v>64</v>
       </c>
@@ -4612,7 +3777,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="89"/>
+      <c r="A9" s="109"/>
       <c r="B9" t="s">
         <v>43</v>
       </c>
@@ -4621,7 +3786,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="90" t="s">
+      <c r="A10" s="110" t="s">
         <v>67</v>
       </c>
       <c r="B10" t="s">
@@ -4632,7 +3797,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="90"/>
+      <c r="A11" s="110"/>
       <c r="B11" t="s">
         <v>70</v>
       </c>
@@ -4641,7 +3806,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="91" t="s">
+      <c r="A12" s="111" t="s">
         <v>72</v>
       </c>
       <c r="B12" t="s">
@@ -4652,7 +3817,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="91"/>
+      <c r="A13" s="111"/>
       <c r="B13" t="s">
         <v>75</v>
       </c>
@@ -4661,7 +3826,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="91"/>
+      <c r="A14" s="111"/>
       <c r="B14" t="s">
         <v>77</v>
       </c>
@@ -4703,17 +3868,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4722,7 +3876,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -4971,14 +4125,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F2B1ADB-E196-4325-983D-4FD97D011467}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F2B1ADB-E196-4325-983D-4FD97D011467}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
--- a/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="698" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{512ACBC7-8CD6-498B-83C0-B9E93875DDFA}"/>
+  <xr:revisionPtr revIDLastSave="703" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC81C01-DB30-4E3D-AEF9-9D01207E13B8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="95">
   <si>
     <t>Project ID</t>
   </si>
@@ -152,50 +152,53 @@
     <t>GCF-Managing Climate Change Induced Water Shortages</t>
   </si>
   <si>
+    <t>https://open.undp.org/projects/00094293</t>
+  </si>
+  <si>
+    <t>Water Services</t>
+  </si>
+  <si>
+    <t>Beneficiaries of the Project - 105,000 people
+No. of Solar PV backed Integrated Water Resource Management system / RO plants</t>
+  </si>
+  <si>
+    <t>GEF</t>
+  </si>
+  <si>
+    <t>VF</t>
+  </si>
+  <si>
+    <t>Project For Developing Sustainable Agricultural Economy</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/00142132</t>
+  </si>
+  <si>
+    <t>500 contract farmers across Maldives</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>Greater Male' area population of 212,138 people
+No. of solar PV backed charging stations available in greater Male' region to support EV public transport network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to the CO: Please provide a more conservative estimate for beneficiaries, not the entire population
+CO Response: The ridership of the EV bus routes is approximately 4000 per week. </t>
+  </si>
+  <si>
+    <t>Agricultural Services</t>
+  </si>
+  <si>
     <t>https://open.undp.org/projects/00094293
 PIMS+</t>
-  </si>
-  <si>
-    <t>Water Services</t>
-  </si>
-  <si>
-    <t>Beneficiaries of the Project - 105,000 people
-No. of Solar PV backed Integrated Water Resource Management system / RO plants</t>
-  </si>
-  <si>
-    <t>GEF</t>
-  </si>
-  <si>
-    <t>VF</t>
-  </si>
-  <si>
-    <t>Project For Developing Sustainable Agricultural Economy</t>
-  </si>
-  <si>
-    <t>https://open.undp.org/projects/00142132</t>
-  </si>
-  <si>
-    <t>500 contract farmers across Maldives</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>Greater Male' area population of 212,138 people
-No. of solar PV backed charging stations available in greater Male' region to support EV public transport network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">to the CO: Please provide a more conservative estimate for beneficiaries, not the entire population
-CO Response: The ridership of the EV bus routes is approximately 4000 per week. </t>
-  </si>
-  <si>
-    <t>Agricultural Services</t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -596,7 +599,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -806,10 +809,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1252,31 +1251,31 @@
       <c r="K1" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="102" t="s">
+      <c r="L1" s="100" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="103" t="s">
+      <c r="M1" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="102" t="s">
+      <c r="N1" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="102" t="s">
+      <c r="O1" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="103" t="s">
+      <c r="P1" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="103" t="s">
+      <c r="Q1" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="104" t="s">
+      <c r="R1" s="102" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="104" t="s">
+      <c r="T1" s="102" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="85" t="s">
@@ -1285,12 +1284,12 @@
     </row>
     <row r="2" spans="1:26" s="6" customFormat="1" ht="137.25">
       <c r="A2" s="88">
-        <v>130247</v>
-      </c>
-      <c r="B2" s="91" t="s">
+        <v>141744</v>
+      </c>
+      <c r="B2" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="94" t="s">
+      <c r="C2" s="92" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="83">
@@ -1315,11 +1314,11 @@
         <v>26</v>
       </c>
       <c r="K2" s="66"/>
-      <c r="L2" s="105" t="s">
+      <c r="L2" s="103" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="23"/>
-      <c r="N2" s="106" t="s">
+      <c r="N2" s="104" t="s">
         <v>28</v>
       </c>
       <c r="O2" s="23"/>
@@ -1341,7 +1340,6 @@
       </c>
     </row>
     <row r="3" spans="1:26" s="7" customFormat="1" ht="45.75">
-      <c r="A3" s="89"/>
       <c r="B3" s="74"/>
       <c r="C3" s="74"/>
       <c r="D3" s="71"/>
@@ -1362,11 +1360,11 @@
       </c>
       <c r="J3" s="17"/>
       <c r="K3" s="86"/>
-      <c r="L3" s="105" t="s">
+      <c r="L3" s="103" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="23"/>
-      <c r="N3" s="106" t="s">
+      <c r="N3" s="104" t="s">
         <v>28</v>
       </c>
       <c r="O3" s="23"/>
@@ -1386,26 +1384,25 @@
       </c>
     </row>
     <row r="4" spans="1:26" s="7" customFormat="1" ht="45.75">
-      <c r="A4" s="90"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="95"/>
-      <c r="D4" s="93"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="91"/>
       <c r="E4" s="80"/>
-      <c r="F4" s="96" t="s">
+      <c r="F4" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="97">
+      <c r="G4" s="95">
         <v>5</v>
       </c>
-      <c r="H4" s="97"/>
-      <c r="I4" s="98"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="96"/>
       <c r="J4" s="71"/>
       <c r="K4" s="84"/>
-      <c r="L4" s="105" t="s">
+      <c r="L4" s="103" t="s">
         <v>27</v>
       </c>
       <c r="M4" s="23"/>
-      <c r="N4" s="106" t="s">
+      <c r="N4" s="104" t="s">
         <v>28</v>
       </c>
       <c r="O4" s="23"/>
@@ -1456,11 +1453,11 @@
         <v>39</v>
       </c>
       <c r="K5" s="73"/>
-      <c r="L5" s="105" t="s">
+      <c r="L5" s="103" t="s">
         <v>40</v>
       </c>
       <c r="M5" s="23"/>
-      <c r="N5" s="106" t="s">
+      <c r="N5" s="104" t="s">
         <v>28</v>
       </c>
       <c r="O5" s="23"/>
@@ -1483,7 +1480,7 @@
     </row>
     <row r="6" spans="1:26" s="7" customFormat="1" ht="65.25" customHeight="1">
       <c r="A6" s="8">
-        <v>130474</v>
+        <v>142132</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>41</v>
@@ -1513,11 +1510,11 @@
         <v>26</v>
       </c>
       <c r="K6" s="84"/>
-      <c r="L6" s="105" t="s">
+      <c r="L6" s="103" t="s">
         <v>27</v>
       </c>
       <c r="M6" s="23"/>
-      <c r="N6" s="106" t="s">
+      <c r="N6" s="104" t="s">
         <v>28</v>
       </c>
       <c r="O6" s="23"/>
@@ -1550,7 +1547,7 @@
       <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="C8" s="99"/>
+      <c r="C8" s="97"/>
     </row>
   </sheetData>
   <dataValidations count="10">
@@ -1587,7 +1584,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{F8427973-C397-4925-81CE-9E5A55F828B3}"/>
-    <hyperlink ref="C5" r:id="rId2" display="https://open.undp.org/projects/00094293" xr:uid="{C7DDC491-2558-4E1D-ADAA-4477426A4D68}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{C7DDC491-2558-4E1D-ADAA-4477426A4D68}"/>
     <hyperlink ref="C6" r:id="rId3" xr:uid="{3AA6A34F-1FDA-4182-B54C-0E9DEAD4C7CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1800,7 +1797,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D5" s="70">
         <v>23636364</v>
@@ -2016,58 +2013,58 @@
       <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="107"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="110"/>
+      <c r="A19" s="105"/>
+      <c r="B19" s="106"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="108"/>
       <c r="F19" s="48"/>
       <c r="H19" s="48"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="107"/>
-      <c r="B20" s="108"/>
-      <c r="C20" s="109"/>
-      <c r="D20" s="110"/>
+      <c r="A20" s="105"/>
+      <c r="B20" s="106"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="108"/>
       <c r="F20" s="48"/>
       <c r="H20" s="48"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="107"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="110"/>
+      <c r="A21" s="105"/>
+      <c r="B21" s="106"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="108"/>
       <c r="G21" s="47"/>
       <c r="I21" s="49"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="107"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="110"/>
+      <c r="A22" s="105"/>
+      <c r="B22" s="106"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="108"/>
       <c r="H22"/>
       <c r="I22" s="49"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="107"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="110"/>
+      <c r="A23" s="105"/>
+      <c r="B23" s="106"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="108"/>
       <c r="F23" s="50"/>
       <c r="G23" s="47"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="107"/>
-      <c r="B24" s="108"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="110"/>
+      <c r="A24" s="105"/>
+      <c r="B24" s="106"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="108"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="107"/>
-      <c r="B25" s="108"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="110"/>
+      <c r="A25" s="105"/>
+      <c r="B25" s="106"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="108"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="53"/>
@@ -2789,10 +2786,10 @@
         <v>1100000</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -2801,7 +2798,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="7" customFormat="1" ht="45.75">
@@ -2813,7 +2810,7 @@
         <v>49</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G3" s="8">
         <v>5</v>
@@ -2872,7 +2869,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D7" s="10">
         <v>23636364</v>
@@ -2881,7 +2878,7 @@
         <v>37</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" s="12">
         <v>5</v>
@@ -2890,7 +2887,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" ht="30.75">
@@ -2910,7 +2907,7 @@
         <v>49</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="8">
         <v>0</v>
@@ -3055,10 +3052,10 @@
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="112"/>
-      <c r="B21" s="111"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="114"/>
+      <c r="A21" s="110"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="112"/>
       <c r="E21" s="24"/>
       <c r="F21" s="25"/>
       <c r="G21" s="26"/>
@@ -3066,10 +3063,10 @@
       <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="112"/>
-      <c r="B22" s="111"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="114"/>
+      <c r="A22" s="110"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="111"/>
+      <c r="D22" s="112"/>
       <c r="E22" s="24"/>
       <c r="F22" s="25"/>
       <c r="G22" s="26"/>
@@ -3077,10 +3074,10 @@
       <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="112"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="113"/>
-      <c r="D23" s="114"/>
+      <c r="A23" s="110"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="112"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -3088,10 +3085,10 @@
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="112"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="113"/>
-      <c r="D24" s="114"/>
+      <c r="A24" s="110"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="111"/>
+      <c r="D24" s="112"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="26"/>
@@ -3099,10 +3096,10 @@
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="112"/>
-      <c r="B25" s="111"/>
-      <c r="C25" s="113"/>
-      <c r="D25" s="114"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="112"/>
       <c r="E25" s="24"/>
       <c r="F25" s="29"/>
       <c r="G25" s="23"/>
@@ -3110,10 +3107,10 @@
       <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="112"/>
-      <c r="B26" s="111"/>
-      <c r="C26" s="113"/>
-      <c r="D26" s="114"/>
+      <c r="A26" s="110"/>
+      <c r="B26" s="109"/>
+      <c r="C26" s="111"/>
+      <c r="D26" s="112"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="26"/>
@@ -3121,10 +3118,10 @@
       <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="112"/>
-      <c r="B27" s="111"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="114"/>
+      <c r="A27" s="110"/>
+      <c r="B27" s="109"/>
+      <c r="C27" s="111"/>
+      <c r="D27" s="112"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="26"/>
@@ -3785,179 +3782,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="100" t="s">
+      <c r="B1" s="98" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="115" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="101" t="s">
+      <c r="A2" s="113" t="s">
         <v>58</v>
       </c>
+      <c r="B2" s="99" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="115" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="101" t="s">
+      <c r="A3" s="113" t="s">
         <v>60</v>
       </c>
+      <c r="B3" s="99" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="115" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="101" t="s">
+      <c r="A4" s="113" t="s">
         <v>62</v>
       </c>
+      <c r="B4" s="99" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="115" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="101" t="s">
+      <c r="A5" s="113" t="s">
         <v>64</v>
       </c>
+      <c r="B5" s="99" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="45.75">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="101" t="s">
-        <v>65</v>
+      <c r="B6" s="99" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="115" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="101" t="s">
+      <c r="A7" s="113" t="s">
         <v>67</v>
       </c>
+      <c r="B7" s="99" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="101" t="s">
-        <v>68</v>
+      <c r="B8" s="99" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="101" t="s">
+      <c r="A9" s="113" t="s">
         <v>70</v>
       </c>
+      <c r="B9" s="99" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="116" t="s">
-        <v>71</v>
+      <c r="B10" s="114" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="115" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="116" t="s">
+      <c r="A11" s="113" t="s">
         <v>73</v>
       </c>
+      <c r="B11" s="114" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="115" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="101" t="s">
+      <c r="A12" s="113" t="s">
         <v>75</v>
       </c>
+      <c r="B12" s="99" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="115" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="116" t="s">
-        <v>76</v>
+      <c r="A13" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="114" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="115" t="s">
-        <v>77</v>
-      </c>
-      <c r="B14" s="116" t="s">
+      <c r="A14" s="113" t="s">
         <v>78</v>
       </c>
+      <c r="B14" s="114" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="115" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="116" t="s">
+      <c r="A15" s="113" t="s">
         <v>80</v>
       </c>
+      <c r="B15" s="114" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="115" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="116" t="s">
+      <c r="A16" s="113" t="s">
         <v>82</v>
       </c>
+      <c r="B16" s="114" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="115" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="101" t="s">
+      <c r="A17" s="113" t="s">
         <v>84</v>
       </c>
+      <c r="B17" s="99" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="115" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="116" t="s">
+      <c r="A18" s="113" t="s">
         <v>86</v>
       </c>
+      <c r="B18" s="114" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="115" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="116" t="s">
+      <c r="A19" s="113" t="s">
         <v>88</v>
       </c>
+      <c r="B19" s="114" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="115" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="116" t="s">
+      <c r="A20" s="113" t="s">
         <v>90</v>
       </c>
+      <c r="B20" s="114" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="115" t="s">
+      <c r="A21" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="117" t="s">
-        <v>91</v>
+      <c r="B21" s="115" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="115" t="s">
-        <v>92</v>
-      </c>
-      <c r="B22" s="116" t="s">
+      <c r="A22" s="113" t="s">
         <v>93</v>
+      </c>
+      <c r="B22" s="114" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3966,17 +3963,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -4001,6 +3989,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4080,6 +4069,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -4223,6 +4217,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4235,11 +4238,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A45A6CB-C896-45F7-BD50-B705618876B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F2B1ADB-E196-4325-983D-4FD97D011467}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="703" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC81C01-DB30-4E3D-AEF9-9D01207E13B8}"/>
+  <xr:revisionPtr revIDLastSave="717" documentId="8_{8CAB50D8-CF81-BC4A-BCD6-641596546354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F25F062-D2C8-458C-8FD8-A77A896B9CFF}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="5" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="4" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="109">
   <si>
     <t>Project ID</t>
   </si>
@@ -162,12 +162,15 @@
 No. of Solar PV backed Integrated Water Resource Management system / RO plants</t>
   </si>
   <si>
-    <t>GEF</t>
+    <t>GCF</t>
   </si>
   <si>
     <t>VF</t>
   </si>
   <si>
+    <t>Enactment of Water and Sanitation Act (legislation) that states all water production in Maldives needs to be powered via renewable energy by 2025. Potentially benefiting all residents of Maldives to access clean energy powered water.</t>
+  </si>
+  <si>
     <t>Project For Developing Sustainable Agricultural Economy</t>
   </si>
   <si>
@@ -175,6 +178,42 @@
   </si>
   <si>
     <t>500 contract farmers across Maldives</t>
+  </si>
+  <si>
+    <t>Energy related results from Maldives are missing. Giving some of the results below. Requesting guidance on updating the results.</t>
+  </si>
+  <si>
+    <t>A. GCF funded Supporting vulnerable communities in Maldives to manage climate change induced water shortages project.</t>
+  </si>
+  <si>
+    <t>1. Provision of water via renewable energy 4 islands (total solar 100 kWh capacity installed) total of 19,871 people (9,432 females, 10,439 males) estimated 200 tonnes carbon reduction per annum.</t>
+  </si>
+  <si>
+    <t>2. Enactment of Water and Sanitation Act (legislation) that states all water production in Maldives needs to be powered via renewable energy by 2025. Potentially benefiting all residents of Maldives to access clean energy powered water.</t>
+  </si>
+  <si>
+    <t>B. Climate Promise 2 - Net Zero Emissions project</t>
+  </si>
+  <si>
+    <t>1. Air Quality Monitoring system tracking air pollution (direct beneficiaries 212138 people, indirectly benefits 302994 people) 21 people trained.</t>
+  </si>
+  <si>
+    <t>2. Solar powered drip irrigation systems benefiting 12 farmers (12 systems and 12 individuals trained).</t>
+  </si>
+  <si>
+    <t>3. 2 Solar powered cold storages with 0.48 megawatt solar power installed. Direct benefits 10 farmers, indirect benefits to 15891 residents.</t>
+  </si>
+  <si>
+    <t>4. Solar panels and charging stations for EV bus route. Estimated CO2 reduction 2.033 tonnes per annum. Weekly bus ridership 4524 riders. Indirect benefits to 212138 people. 10 people trained.</t>
+  </si>
+  <si>
+    <t>C. Project for Developing Sustainable Agricultural Economy</t>
+  </si>
+  <si>
+    <t>1. Establishment of Solar Powered cold storages</t>
+  </si>
+  <si>
+    <t>2. Solar and diesel hybrid agri boat</t>
   </si>
   <si>
     <t>Category</t>
@@ -199,6 +238,9 @@
   <si>
     <t>https://open.undp.org/projects/00094293
 PIMS+</t>
+  </si>
+  <si>
+    <t>GEF</t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -356,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,6 +481,12 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -466,7 +514,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -594,12 +642,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -853,6 +910,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,6 +940,9 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1191,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F57C0583-E09D-4D51-BD15-84D2EB417CAA}">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -1422,10 +1489,10 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="7" customFormat="1" ht="45.75">
-      <c r="A5" s="71">
+      <c r="A5" s="36">
         <v>94293</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="105" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="69" t="s">
@@ -1478,45 +1545,25 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="7" customFormat="1" ht="65.25" customHeight="1">
-      <c r="A6" s="8">
-        <v>142132</v>
-      </c>
-      <c r="B6" s="11" t="s">
+    <row r="6" spans="1:26" s="7" customFormat="1" ht="60.75">
+      <c r="A6" s="71"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="52"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="10">
-        <v>2500000</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>500</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="84"/>
-      <c r="L6" s="103" t="s">
-        <v>27</v>
-      </c>
+      <c r="J6" s="36"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="103"/>
       <c r="M6" s="23"/>
-      <c r="N6" s="104" t="s">
-        <v>28</v>
-      </c>
+      <c r="N6" s="104"/>
       <c r="O6" s="23"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="23"/>
@@ -1524,68 +1571,256 @@
       <c r="S6" s="27"/>
       <c r="T6" s="23"/>
       <c r="U6" s="27"/>
-      <c r="W6" s="17" t="s">
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+    </row>
+    <row r="7" spans="1:26" s="7" customFormat="1">
+      <c r="A7" s="107"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="27"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+    </row>
+    <row r="8" spans="1:26" s="7" customFormat="1" ht="65.25" customHeight="1">
+      <c r="A8" s="106">
+        <v>142132</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2500000</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>500</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="84"/>
+      <c r="L8" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="22" t="s">
+      <c r="M8" s="23"/>
+      <c r="N8" s="104" t="s">
+        <v>28</v>
+      </c>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="27"/>
+      <c r="W8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="Z6" s="22" t="s">
+      <c r="Z8" s="22" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="7" customFormat="1">
-      <c r="A7" s="39"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="42"/>
-    </row>
-    <row r="8" spans="1:26">
-      <c r="C8" s="97"/>
+    <row r="9" spans="1:26" s="7" customFormat="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="42"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="C10" s="97"/>
+    </row>
+    <row r="14" spans="1:26" ht="57.75" customHeight="1">
+      <c r="B14" s="116" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="B15" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="B16" s="116" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" s="116" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="116"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="116"/>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="116" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="116" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" s="116" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="116" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="116" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="116" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+  </mergeCells>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6" xr:uid="{59D04436-BB66-4C68-AE9B-2757F2553F47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q8" xr:uid="{59D04436-BB66-4C68-AE9B-2757F2553F47}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P6" xr:uid="{09F08509-131A-4929-AC18-1D4958F55ABA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P8" xr:uid="{09F08509-131A-4929-AC18-1D4958F55ABA}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y6 N2:N6" xr:uid="{640EB288-81BF-4916-BA00-342C0ED3C2AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y8 N2:N8" xr:uid="{640EB288-81BF-4916-BA00-342C0ED3C2AD}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z6" xr:uid="{7AFCE844-73E4-424F-9F4E-C6E3F69638B0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2:Z8" xr:uid="{7AFCE844-73E4-424F-9F4E-C6E3F69638B0}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O6" xr:uid="{008E5358-F11D-4B9D-BE42-2A5BEDF79C11}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O8" xr:uid="{008E5358-F11D-4B9D-BE42-2A5BEDF79C11}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L6" xr:uid="{44742454-7B8B-470B-8AA4-0A0A6A763027}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L8" xr:uid="{44742454-7B8B-470B-8AA4-0A0A6A763027}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M6" xr:uid="{F0DB7161-5D27-423F-BE9D-7EBF19E10057}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M8" xr:uid="{F0DB7161-5D27-423F-BE9D-7EBF19E10057}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T6" xr:uid="{0DECFE32-8639-45C8-9F93-A35E045376A8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T8" xr:uid="{0DECFE32-8639-45C8-9F93-A35E045376A8}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{D34AB976-A808-4BE4-8D2B-230742AD09D7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R8" xr:uid="{D34AB976-A808-4BE4-8D2B-230742AD09D7}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S6" xr:uid="{7DE1EABB-1D47-4CF7-A0BE-EBA42D2873FB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S8" xr:uid="{7DE1EABB-1D47-4CF7-A0BE-EBA42D2873FB}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{F8427973-C397-4925-81CE-9E5A55F828B3}"/>
     <hyperlink ref="C5" r:id="rId2" xr:uid="{C7DDC491-2558-4E1D-ADAA-4477426A4D68}"/>
-    <hyperlink ref="C6" r:id="rId3" xr:uid="{3AA6A34F-1FDA-4182-B54C-0E9DEAD4C7CD}"/>
+    <hyperlink ref="C8" r:id="rId3" xr:uid="{3AA6A34F-1FDA-4182-B54C-0E9DEAD4C7CD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1595,13 +1830,13 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$16</xm:f>
           </x14:formula1>
-          <xm:sqref>E7:E12</xm:sqref>
+          <xm:sqref>E9:E13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EBBD40FD-7F7E-4D98-98B2-21049169C106}">
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E6</xm:sqref>
+          <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1663,10 +1898,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="32" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M1" s="38" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="N1" s="37"/>
       <c r="O1" s="61" t="s">
@@ -1699,7 +1934,7 @@
         <v>1100000</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="F2" s="62" t="s">
         <v>24</v>
@@ -1711,7 +1946,7 @@
         <v>4000</v>
       </c>
       <c r="I2" s="64" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="J2" s="65" t="s">
         <v>26</v>
@@ -1721,7 +1956,7 @@
         <v>27</v>
       </c>
       <c r="M2" s="76" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N2" s="67"/>
       <c r="O2" s="67" t="s">
@@ -1736,7 +1971,7 @@
     </row>
     <row r="3" spans="1:19" s="7" customFormat="1" ht="29.25" customHeight="1">
       <c r="E3" s="80" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>32</v>
@@ -1797,7 +2032,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="69" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D5" s="70">
         <v>23636364</v>
@@ -1818,7 +2053,7 @@
         <v>38</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="K5" s="36"/>
       <c r="L5" s="73" t="s">
@@ -1840,16 +2075,16 @@
         <v>130474</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="10">
         <v>2500000</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>32</v>
@@ -1861,7 +2096,7 @@
         <v>500</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>26</v>
@@ -2013,58 +2248,58 @@
       <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="105"/>
-      <c r="B19" s="106"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="108"/>
+      <c r="A19" s="108"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
       <c r="F19" s="48"/>
       <c r="H19" s="48"/>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="105"/>
-      <c r="B20" s="106"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="108"/>
+      <c r="A20" s="108"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="111"/>
       <c r="F20" s="48"/>
       <c r="H20" s="48"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="105"/>
-      <c r="B21" s="106"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="108"/>
+      <c r="A21" s="108"/>
+      <c r="B21" s="109"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="111"/>
       <c r="G21" s="47"/>
       <c r="I21" s="49"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="105"/>
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="108"/>
+      <c r="A22" s="108"/>
+      <c r="B22" s="109"/>
+      <c r="C22" s="110"/>
+      <c r="D22" s="111"/>
       <c r="H22"/>
       <c r="I22" s="49"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="105"/>
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="108"/>
+      <c r="A23" s="108"/>
+      <c r="B23" s="109"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="111"/>
       <c r="F23" s="50"/>
       <c r="G23" s="47"/>
       <c r="H23" s="49"/>
       <c r="I23" s="49"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="105"/>
-      <c r="B24" s="106"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="108"/>
+      <c r="A24" s="108"/>
+      <c r="B24" s="109"/>
+      <c r="C24" s="110"/>
+      <c r="D24" s="111"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="105"/>
-      <c r="B25" s="106"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="108"/>
+      <c r="A25" s="108"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="111"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="53"/>
@@ -2786,10 +3021,10 @@
         <v>1100000</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="G2" s="8">
         <v>0</v>
@@ -2798,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="75" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="7" customFormat="1" ht="45.75">
@@ -2807,10 +3042,10 @@
       <c r="C3" s="9"/>
       <c r="D3" s="10"/>
       <c r="E3" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G3" s="8">
         <v>5</v>
@@ -2828,7 +3063,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>34</v>
@@ -2869,7 +3104,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D7" s="10">
         <v>23636364</v>
@@ -2878,7 +3113,7 @@
         <v>37</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G7" s="12">
         <v>5</v>
@@ -2887,7 +3122,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="7" customFormat="1" ht="30.75">
@@ -2895,19 +3130,19 @@
         <v>130474</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" s="10">
         <v>2500000</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G8" s="8">
         <v>0</v>
@@ -2916,7 +3151,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="7" customFormat="1">
@@ -3052,10 +3287,10 @@
       <c r="I20" s="22"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="110"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="112"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="115"/>
       <c r="E21" s="24"/>
       <c r="F21" s="25"/>
       <c r="G21" s="26"/>
@@ -3063,10 +3298,10 @@
       <c r="I21" s="24"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="110"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="112"/>
+      <c r="A22" s="113"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="115"/>
       <c r="E22" s="24"/>
       <c r="F22" s="25"/>
       <c r="G22" s="26"/>
@@ -3074,10 +3309,10 @@
       <c r="I22" s="24"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="110"/>
-      <c r="B23" s="109"/>
-      <c r="C23" s="111"/>
-      <c r="D23" s="112"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="114"/>
+      <c r="D23" s="115"/>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="23"/>
@@ -3085,10 +3320,10 @@
       <c r="I23" s="27"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="110"/>
-      <c r="B24" s="109"/>
-      <c r="C24" s="111"/>
-      <c r="D24" s="112"/>
+      <c r="A24" s="113"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="114"/>
+      <c r="D24" s="115"/>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="26"/>
@@ -3096,10 +3331,10 @@
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="110"/>
-      <c r="B25" s="109"/>
-      <c r="C25" s="111"/>
-      <c r="D25" s="112"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="114"/>
+      <c r="D25" s="115"/>
       <c r="E25" s="24"/>
       <c r="F25" s="29"/>
       <c r="G25" s="23"/>
@@ -3107,10 +3342,10 @@
       <c r="I25" s="27"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="110"/>
-      <c r="B26" s="109"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="112"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="114"/>
+      <c r="D26" s="115"/>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="26"/>
@@ -3118,10 +3353,10 @@
       <c r="I26" s="24"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="110"/>
-      <c r="B27" s="109"/>
-      <c r="C27" s="111"/>
-      <c r="D27" s="112"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="114"/>
+      <c r="D27" s="115"/>
       <c r="E27" s="24"/>
       <c r="F27" s="24"/>
       <c r="G27" s="26"/>
@@ -3790,171 +4025,171 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="113" t="s">
-        <v>58</v>
+      <c r="A2" s="117" t="s">
+        <v>72</v>
       </c>
       <c r="B2" s="99" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="113" t="s">
-        <v>60</v>
+      <c r="A3" s="117" t="s">
+        <v>74</v>
       </c>
       <c r="B3" s="99" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="113" t="s">
-        <v>62</v>
+      <c r="A4" s="117" t="s">
+        <v>76</v>
       </c>
       <c r="B4" s="99" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="113" t="s">
-        <v>64</v>
+      <c r="A5" s="117" t="s">
+        <v>78</v>
       </c>
       <c r="B5" s="99" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45.75">
+      <c r="A6" s="117" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="117" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="99" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30.75">
+      <c r="A8" s="117" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="99" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="30.75">
+      <c r="A9" s="117" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="99" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30.75">
+      <c r="A10" s="117" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="118" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="118" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="30.75">
+      <c r="A12" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="99" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="117" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="45.75">
-      <c r="A6" s="113" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="99" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="113" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="99" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30.75">
-      <c r="A8" s="113" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="99" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30.75">
-      <c r="A9" s="113" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="99" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="113" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="114" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="113" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="114" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30.75">
-      <c r="A12" s="113" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="99" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="113" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>77</v>
+      <c r="B13" s="118" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="113" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="114" t="s">
-        <v>79</v>
+      <c r="A14" s="117" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="118" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="113" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="114" t="s">
-        <v>81</v>
+      <c r="A15" s="117" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="118" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="113" t="s">
-        <v>82</v>
-      </c>
-      <c r="B16" s="114" t="s">
-        <v>83</v>
+      <c r="A16" s="117" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="118" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="113" t="s">
-        <v>84</v>
+      <c r="A17" s="117" t="s">
+        <v>98</v>
       </c>
       <c r="B17" s="99" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="113" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="114" t="s">
-        <v>87</v>
+      <c r="A18" s="117" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="118" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="45.75">
-      <c r="A19" s="113" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="114" t="s">
-        <v>89</v>
+      <c r="A19" s="117" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="118" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="113" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" s="114" t="s">
-        <v>91</v>
+      <c r="A20" s="117" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" s="118" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
-      <c r="A21" s="113" t="s">
+      <c r="A21" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="115" t="s">
-        <v>92</v>
+      <c r="B21" s="119" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="113" t="s">
-        <v>93</v>
-      </c>
-      <c r="B22" s="114" t="s">
-        <v>94</v>
+      <c r="A22" s="117" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="118" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3963,6 +4198,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -4217,15 +4461,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4238,11 +4473,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A45A6CB-C896-45F7-BD50-B705618876B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A45A6CB-C896-45F7-BD50-B705618876B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Maldives - Energy Projects.xlsx
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -584,16 +584,12 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -677,6 +673,46 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L8" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L11" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1325,15 +1361,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K5" s="95" t="n">
+      <c r="K5" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="121" t="n"/>
-      <c r="M5" s="122" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M5" s="96" t="n"/>
       <c r="N5" s="71" t="n"/>
       <c r="O5" s="84" t="n"/>
       <c r="P5" s="113" t="n"/>
@@ -1367,9 +1399,9 @@
       <c r="D6" s="70" t="n">
         <v>23636364</v>
       </c>
-      <c r="E6" s="123" t="n"/>
-      <c r="F6" s="123" t="n"/>
-      <c r="G6" s="123" t="n"/>
+      <c r="E6" s="122" t="n"/>
+      <c r="F6" s="122" t="n"/>
+      <c r="G6" s="122" t="n"/>
       <c r="H6" s="70" t="inlineStr">
         <is>
           <t>VF</t>
@@ -1490,15 +1522,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K8" s="57" t="n">
+      <c r="K8" s="123" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="124" t="n"/>
-      <c r="M8" s="125" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M8" s="72" t="n"/>
       <c r="N8" s="36" t="n"/>
       <c r="O8" s="73" t="n"/>
       <c r="P8" s="113" t="n"/>
@@ -1562,9 +1590,9 @@
       <c r="D10" s="10" t="n">
         <v>2500000</v>
       </c>
-      <c r="E10" s="126" t="n"/>
-      <c r="F10" s="126" t="n"/>
-      <c r="G10" s="126" t="n"/>
+      <c r="E10" s="125" t="n"/>
+      <c r="F10" s="125" t="n"/>
+      <c r="G10" s="125" t="n"/>
       <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -1646,15 +1674,11 @@
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="121" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="121" t="n"/>
-      <c r="M11" s="127" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
+      <c r="M11" s="14" t="n"/>
       <c r="N11" s="17" t="n"/>
       <c r="O11" s="84" t="n"/>
       <c r="P11" s="113" t="n"/>
@@ -1729,21 +1753,7 @@
       <c r="B28" s="116" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B14:E14"/>
-  </mergeCells>
-  <dataValidations count="13">
+  <dataValidations count="11">
     <dataValidation sqref="Q2:Q8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -1777,17 +1787,12 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3386,10 +3391,10 @@
       <c r="I21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="128" t="n"/>
-      <c r="B22" s="128" t="n"/>
-      <c r="C22" s="128" t="n"/>
-      <c r="D22" s="128" t="n"/>
+      <c r="A22" s="126" t="n"/>
+      <c r="B22" s="126" t="n"/>
+      <c r="C22" s="126" t="n"/>
+      <c r="D22" s="126" t="n"/>
       <c r="E22" s="24" t="n"/>
       <c r="F22" s="25" t="n"/>
       <c r="G22" s="26" t="n"/>
@@ -3397,10 +3402,10 @@
       <c r="I22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="128" t="n"/>
-      <c r="B23" s="128" t="n"/>
-      <c r="C23" s="128" t="n"/>
-      <c r="D23" s="128" t="n"/>
+      <c r="A23" s="126" t="n"/>
+      <c r="B23" s="126" t="n"/>
+      <c r="C23" s="126" t="n"/>
+      <c r="D23" s="126" t="n"/>
       <c r="E23" s="24" t="n"/>
       <c r="F23" s="24" t="n"/>
       <c r="G23" s="113" t="n"/>
@@ -3408,10 +3413,10 @@
       <c r="I23" s="27" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="128" t="n"/>
-      <c r="B24" s="128" t="n"/>
-      <c r="C24" s="128" t="n"/>
-      <c r="D24" s="128" t="n"/>
+      <c r="A24" s="126" t="n"/>
+      <c r="B24" s="126" t="n"/>
+      <c r="C24" s="126" t="n"/>
+      <c r="D24" s="126" t="n"/>
       <c r="E24" s="24" t="n"/>
       <c r="F24" s="24" t="n"/>
       <c r="G24" s="26" t="n"/>
@@ -3419,10 +3424,10 @@
       <c r="I24" s="27" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="128" t="n"/>
-      <c r="B25" s="128" t="n"/>
-      <c r="C25" s="128" t="n"/>
-      <c r="D25" s="128" t="n"/>
+      <c r="A25" s="126" t="n"/>
+      <c r="B25" s="126" t="n"/>
+      <c r="C25" s="126" t="n"/>
+      <c r="D25" s="126" t="n"/>
       <c r="E25" s="24" t="n"/>
       <c r="F25" s="29" t="n"/>
       <c r="G25" s="113" t="n"/>
@@ -3430,10 +3435,10 @@
       <c r="I25" s="27" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="128" t="n"/>
-      <c r="B26" s="128" t="n"/>
-      <c r="C26" s="128" t="n"/>
-      <c r="D26" s="128" t="n"/>
+      <c r="A26" s="126" t="n"/>
+      <c r="B26" s="126" t="n"/>
+      <c r="C26" s="126" t="n"/>
+      <c r="D26" s="126" t="n"/>
       <c r="E26" s="24" t="n"/>
       <c r="F26" s="24" t="n"/>
       <c r="G26" s="26" t="n"/>
@@ -3441,10 +3446,10 @@
       <c r="I26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="129" t="n"/>
-      <c r="B27" s="129" t="n"/>
-      <c r="C27" s="129" t="n"/>
-      <c r="D27" s="129" t="n"/>
+      <c r="A27" s="127" t="n"/>
+      <c r="B27" s="127" t="n"/>
+      <c r="C27" s="127" t="n"/>
+      <c r="D27" s="127" t="n"/>
       <c r="E27" s="24" t="n"/>
       <c r="F27" s="24" t="n"/>
       <c r="G27" s="26" t="n"/>
@@ -4097,288 +4102,288 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="130" t="inlineStr">
+      <c r="A1" s="128" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="130" t="inlineStr">
+      <c r="B1" s="128" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30.75" customHeight="1">
-      <c r="A2" s="131" t="inlineStr">
+      <c r="A2" s="129" t="inlineStr">
         <is>
           <t>Electricity Access</t>
         </is>
       </c>
-      <c r="B2" s="131" t="inlineStr">
+      <c r="B2" s="129" t="inlineStr">
         <is>
           <t>Number of people, disaggregated by sex, who gain access to clean electricity (direct access to electricity, lighting, cooling, etc.).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="129" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="B3" s="131" t="inlineStr">
+      <c r="B3" s="129" t="inlineStr">
         <is>
           <t>Installed renewable or clean-energy power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="129" t="inlineStr">
         <is>
           <t>Energy Storage (MW)</t>
         </is>
       </c>
-      <c r="B4" s="131" t="inlineStr">
+      <c r="B4" s="129" t="inlineStr">
         <is>
           <t>Installed energy storage power capacity added, in MW.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="129" t="inlineStr">
         <is>
           <t>Clean Cooking</t>
         </is>
       </c>
-      <c r="B5" s="131" t="inlineStr">
+      <c r="B5" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean cooking (direct access to clean cook stoves, clean fuels, biomass, etc.).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45.75" customHeight="1">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="129" t="inlineStr">
         <is>
           <t>Clean Heating</t>
         </is>
       </c>
-      <c r="B6" s="131" t="inlineStr">
+      <c r="B6" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean heating (direct access to clean electric heaters, clean fuels, etc.).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="129" t="inlineStr">
         <is>
           <t>Agriculture and Food System</t>
         </is>
       </c>
-      <c r="B7" s="131" t="inlineStr">
+      <c r="B7" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to clean, affordable, and sustainable energy for agricultural and food-system activities.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="129" t="inlineStr">
         <is>
           <t>Health Services</t>
         </is>
       </c>
-      <c r="B8" s="131" t="inlineStr">
+      <c r="B8" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to health care facilities through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="129" t="inlineStr">
         <is>
           <t>Water Services</t>
         </is>
       </c>
-      <c r="B9" s="131" t="inlineStr">
+      <c r="B9" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to water services through clean energy systems.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="129" t="inlineStr">
         <is>
           <t>Education Services</t>
         </is>
       </c>
-      <c r="B10" s="131" t="inlineStr">
+      <c r="B10" s="129" t="inlineStr">
         <is>
           <t>Number of people who gain access to education services through clean energy systems, including students and teachers.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="129" t="inlineStr">
         <is>
           <t>Transportation and E-mobility Services</t>
         </is>
       </c>
-      <c r="B11" s="131" t="inlineStr">
+      <c r="B11" s="129" t="inlineStr">
         <is>
           <t>Number of people served or energy saved from transport and e-mobility interventions, such as electric vehicles or charging stations.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="129" t="inlineStr">
         <is>
           <t>Energy Efficiency Services</t>
         </is>
       </c>
-      <c r="B12" s="131" t="inlineStr">
+      <c r="B12" s="129" t="inlineStr">
         <is>
           <t>Energy saved from energy-efficiency interventions, such as building or industrial efficiency.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="129" t="inlineStr">
         <is>
           <t>Energy Infrastructure Services</t>
         </is>
       </c>
-      <c r="B13" s="131" t="inlineStr">
+      <c r="B13" s="129" t="inlineStr">
         <is>
           <t>Number of people benefiting from energy infrastructure interventions, such as streetlights, transmission, and distribution lines.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="129" t="inlineStr">
         <is>
           <t>Other Energy Services</t>
         </is>
       </c>
-      <c r="B14" s="131" t="inlineStr">
+      <c r="B14" s="129" t="inlineStr">
         <is>
           <t>Access to other energy services not captured by the categories above.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="129" t="inlineStr">
         <is>
           <t>Financing support</t>
         </is>
       </c>
-      <c r="B15" s="131" t="inlineStr">
+      <c r="B15" s="129" t="inlineStr">
         <is>
           <t>Support for the development of the energy market ecosystem.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="129" t="inlineStr">
         <is>
           <t>Medium Enterprises</t>
         </is>
       </c>
-      <c r="B16" s="131" t="inlineStr">
+      <c r="B16" s="129" t="inlineStr">
         <is>
           <t>Support for the development of medium enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="129" t="inlineStr">
         <is>
           <t>Small Enterprises</t>
         </is>
       </c>
-      <c r="B17" s="131" t="inlineStr">
+      <c r="B17" s="129" t="inlineStr">
         <is>
           <t>Support for the development of small enterprises in the energy transition market.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="129" t="inlineStr">
         <is>
           <t>Capacity Building Training</t>
         </is>
       </c>
-      <c r="B18" s="131" t="inlineStr">
+      <c r="B18" s="129" t="inlineStr">
         <is>
           <t>Number of people benefiting from training on energy business, energy finance, or related implementation capacity.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45.75" customHeight="1">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="129" t="inlineStr">
         <is>
           <t>Entrepreneurship Training</t>
         </is>
       </c>
-      <c r="B19" s="131" t="inlineStr">
+      <c r="B19" s="129" t="inlineStr">
         <is>
           <t>Training for enterprises on the energy business, assumed to result in direct beneficiaries.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="129" t="inlineStr">
         <is>
           <t>Market Intervention</t>
         </is>
       </c>
-      <c r="B20" s="131" t="inlineStr">
+      <c r="B20" s="129" t="inlineStr">
         <is>
           <t>Volume of investment leveraged or barriers removed for clean, reliable, affordable, and sustainable energy solutions.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30.75" customHeight="1">
-      <c r="A21" s="131" t="inlineStr">
+      <c r="A21" s="129" t="inlineStr">
         <is>
           <t>Campaign Participant</t>
         </is>
       </c>
-      <c r="B21" s="131" t="inlineStr">
+      <c r="B21" s="129" t="inlineStr">
         <is>
           <t>Individuals who participate in advocacy or awareness campaigns on energy.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="inlineStr">
+      <c r="A22" s="129" t="inlineStr">
         <is>
           <t>Policy or Regulatory Framework</t>
         </is>
       </c>
-      <c r="B22" s="131" t="inlineStr">
+      <c r="B22" s="129" t="inlineStr">
         <is>
           <t>Policies, regulations, strategies, plans, or frameworks developed, approved, implemented, or strengthened.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="131" t="inlineStr">
+      <c r="A23" s="129" t="inlineStr">
         <is>
           <t>GHG Emissions Reduction</t>
         </is>
       </c>
-      <c r="B23" s="131" t="inlineStr">
+      <c r="B23" s="129" t="inlineStr">
         <is>
           <t>Greenhouse gas emissions reduced or mitigated, in tCO2e.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="131" t="inlineStr">
+      <c r="A24" s="129" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B24" s="131" t="inlineStr">
+      <c r="B24" s="129" t="inlineStr">
         <is>
           <t>Energy-related output that does not fit the standard categories above.</t>
         </is>
